--- a/artfynd/A 27703-2023 artfynd.xlsx
+++ b/artfynd/A 27703-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27703-2023 artfynd.xlsx
+++ b/artfynd/A 27703-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114459079</v>
+        <v>114458877</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460807</v>
+        <v>460741</v>
       </c>
       <c r="R2" t="n">
-        <v>6474521</v>
+        <v>6474561</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,19 +781,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114459058</v>
+        <v>114458965</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460746</v>
+        <v>460779</v>
       </c>
       <c r="R3" t="n">
-        <v>6474596</v>
+        <v>6474586</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +892,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114459078</v>
+        <v>114458968</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460792</v>
+        <v>460753</v>
       </c>
       <c r="R4" t="n">
-        <v>6474530</v>
+        <v>6474552</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +967,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,19 +1003,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114459042</v>
+        <v>114458969</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1063,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460824</v>
+        <v>460755</v>
       </c>
       <c r="R5" t="n">
-        <v>6474598</v>
+        <v>6474545</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,12 +1068,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,19 +1114,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114459073</v>
+        <v>114458970</v>
       </c>
       <c r="B6" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1174,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460779</v>
+        <v>460794</v>
       </c>
       <c r="R6" t="n">
-        <v>6474536</v>
+        <v>6474550</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,6 +1185,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,19 +1225,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114459087</v>
+        <v>114458971</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1285,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460760</v>
+        <v>460817</v>
       </c>
       <c r="R7" t="n">
-        <v>6474595</v>
+        <v>6474535</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,19 +1336,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114459066</v>
+        <v>114458974</v>
       </c>
       <c r="B8" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1396,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460696</v>
+        <v>460820</v>
       </c>
       <c r="R8" t="n">
-        <v>6474532</v>
+        <v>6474529</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,7 +1411,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,15 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114459240</v>
+        <v>114458976</v>
       </c>
       <c r="B9" t="n">
-        <v>91232</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1512,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460697</v>
+        <v>460840</v>
       </c>
       <c r="R9" t="n">
-        <v>6474537</v>
+        <v>6474632</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,12 +1512,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,19 +1553,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114459076</v>
+        <v>114459001</v>
       </c>
       <c r="B10" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1623,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460783</v>
+        <v>460685</v>
       </c>
       <c r="R10" t="n">
-        <v>6474520</v>
+        <v>6474595</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1653,17 +1618,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,19 +1659,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114459015</v>
+        <v>114459003</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1739,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460747</v>
+        <v>460697</v>
       </c>
       <c r="R11" t="n">
-        <v>6474563</v>
+        <v>6474598</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,12 +1724,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,15 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114458877</v>
+        <v>114459005</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460741</v>
+        <v>460715</v>
       </c>
       <c r="R12" t="n">
-        <v>6474561</v>
+        <v>6474585</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1880,12 +1830,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,19 +1871,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114459037</v>
+        <v>114459007</v>
       </c>
       <c r="B13" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1961,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460818</v>
+        <v>460799</v>
       </c>
       <c r="R13" t="n">
-        <v>6474520</v>
+        <v>6474563</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1991,12 +1936,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,19 +1977,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114458965</v>
+        <v>114459008</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2072,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460779</v>
+        <v>460781</v>
       </c>
       <c r="R14" t="n">
-        <v>6474586</v>
+        <v>6474563</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2102,17 +2042,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,19 +2083,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114459016</v>
+        <v>114459010</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2188,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460746</v>
+        <v>460803</v>
       </c>
       <c r="R15" t="n">
-        <v>6474580</v>
+        <v>6474577</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2259,19 +2189,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114459038</v>
+        <v>114459013</v>
       </c>
       <c r="B16" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2299,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460815</v>
+        <v>460756</v>
       </c>
       <c r="R16" t="n">
-        <v>6474515</v>
+        <v>6474585</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2370,19 +2295,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114459088</v>
+        <v>114459015</v>
       </c>
       <c r="B17" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2410,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460808</v>
+        <v>460747</v>
       </c>
       <c r="R17" t="n">
-        <v>6474518</v>
+        <v>6474563</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2446,11 +2366,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>flera svampkroppar runt äldre tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,19 +2401,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114459027</v>
+        <v>114459016</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2526,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460750</v>
+        <v>460746</v>
       </c>
       <c r="R18" t="n">
-        <v>6474545</v>
+        <v>6474580</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2597,19 +2507,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114459055</v>
+        <v>114459017</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2637,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460764</v>
+        <v>460715</v>
       </c>
       <c r="R19" t="n">
-        <v>6474490</v>
+        <v>6474607</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2667,12 +2572,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,19 +2613,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114459070</v>
+        <v>114459018</v>
       </c>
       <c r="B20" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2748,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460673</v>
+        <v>460698</v>
       </c>
       <c r="R20" t="n">
-        <v>6474452</v>
+        <v>6474615</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2784,11 +2684,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>riktigt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,19 +2719,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114459036</v>
+        <v>114459019</v>
       </c>
       <c r="B21" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2864,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460822</v>
+        <v>460697</v>
       </c>
       <c r="R21" t="n">
-        <v>6474531</v>
+        <v>6474615</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2935,15 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114459269</v>
+        <v>114459020</v>
       </c>
       <c r="B22" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460764</v>
+        <v>460679</v>
       </c>
       <c r="R22" t="n">
-        <v>6474490</v>
+        <v>6474602</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3005,17 +2890,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>flera stora ex.</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,19 +2931,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114459072</v>
+        <v>114459021</v>
       </c>
       <c r="B23" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3091,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460703</v>
+        <v>460677</v>
       </c>
       <c r="R23" t="n">
-        <v>6474488</v>
+        <v>6474594</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3162,19 +3037,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114459008</v>
+        <v>114459022</v>
       </c>
       <c r="B24" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3202,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460781</v>
+        <v>460689</v>
       </c>
       <c r="R24" t="n">
-        <v>6474563</v>
+        <v>6474579</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3232,12 +3102,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3273,19 +3143,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114459028</v>
+        <v>114459023</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3313,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460763</v>
+        <v>460706</v>
       </c>
       <c r="R25" t="n">
-        <v>6474554</v>
+        <v>6474574</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3384,19 +3249,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>114458970</v>
+        <v>114459024</v>
       </c>
       <c r="B26" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3424,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460794</v>
+        <v>460724</v>
       </c>
       <c r="R26" t="n">
-        <v>6474550</v>
+        <v>6474568</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3460,11 +3320,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,19 +3355,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114459035</v>
+        <v>114459026</v>
       </c>
       <c r="B27" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3540,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460820</v>
+        <v>460730</v>
       </c>
       <c r="R27" t="n">
-        <v>6474530</v>
+        <v>6474556</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3611,19 +3461,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114459068</v>
+        <v>114459027</v>
       </c>
       <c r="B28" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3651,10 +3496,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460680</v>
+        <v>460750</v>
       </c>
       <c r="R28" t="n">
-        <v>6474546</v>
+        <v>6474545</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3722,19 +3567,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>114459026</v>
+        <v>114459028</v>
       </c>
       <c r="B29" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3762,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460730</v>
+        <v>460763</v>
       </c>
       <c r="R29" t="n">
-        <v>6474556</v>
+        <v>6474554</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3833,19 +3673,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>114459022</v>
+        <v>114459029</v>
       </c>
       <c r="B30" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3873,10 +3708,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460689</v>
+        <v>460758</v>
       </c>
       <c r="R30" t="n">
-        <v>6474579</v>
+        <v>6474546</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3947,16 +3782,11 @@
         <v>114459031</v>
       </c>
       <c r="B31" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4055,19 +3885,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>114459077</v>
+        <v>114459032</v>
       </c>
       <c r="B32" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4095,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460787</v>
+        <v>460782</v>
       </c>
       <c r="R32" t="n">
-        <v>6474533</v>
+        <v>6474537</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4166,19 +3991,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>114459050</v>
+        <v>114459033</v>
       </c>
       <c r="B33" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4206,10 +4026,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460648</v>
+        <v>460805</v>
       </c>
       <c r="R33" t="n">
-        <v>6474500</v>
+        <v>6474543</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4236,17 +4056,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4282,19 +4097,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>114459041</v>
+        <v>114459034</v>
       </c>
       <c r="B34" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4322,10 +4132,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460838</v>
+        <v>460812</v>
       </c>
       <c r="R34" t="n">
-        <v>6474598</v>
+        <v>6474536</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4352,12 +4162,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4393,19 +4203,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>114459032</v>
+        <v>114459035</v>
       </c>
       <c r="B35" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4433,10 +4238,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460782</v>
+        <v>460820</v>
       </c>
       <c r="R35" t="n">
-        <v>6474537</v>
+        <v>6474530</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4504,15 +4309,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>114459255</v>
+        <v>114459036</v>
       </c>
       <c r="B36" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4520,21 +4320,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4344,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460638</v>
+        <v>460822</v>
       </c>
       <c r="R36" t="n">
-        <v>6474544</v>
+        <v>6474531</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4615,15 +4415,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>114459270</v>
+        <v>114459037</v>
       </c>
       <c r="B37" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4631,21 +4426,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4655,10 +4450,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460784</v>
+        <v>460818</v>
       </c>
       <c r="R37" t="n">
-        <v>6474507</v>
+        <v>6474520</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4685,12 +4480,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,15 +4521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>114459253</v>
+        <v>114459038</v>
       </c>
       <c r="B38" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4742,21 +4532,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4766,10 +4556,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460692</v>
+        <v>460815</v>
       </c>
       <c r="R38" t="n">
-        <v>6474481</v>
+        <v>6474515</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,12 +4586,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,19 +4627,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>114459056</v>
+        <v>114459040</v>
       </c>
       <c r="B39" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4877,10 +4662,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460800</v>
+        <v>460819</v>
       </c>
       <c r="R39" t="n">
-        <v>6474582</v>
+        <v>6474548</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4907,17 +4692,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4953,19 +4733,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>114459010</v>
+        <v>114459041</v>
       </c>
       <c r="B40" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4993,10 +4768,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460803</v>
+        <v>460838</v>
       </c>
       <c r="R40" t="n">
-        <v>6474577</v>
+        <v>6474598</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5023,12 +4798,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5064,19 +4839,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>114459007</v>
+        <v>114459042</v>
       </c>
       <c r="B41" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5104,10 +4874,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460799</v>
+        <v>460824</v>
       </c>
       <c r="R41" t="n">
-        <v>6474563</v>
+        <v>6474598</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5175,19 +4945,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>114459013</v>
+        <v>114459043</v>
       </c>
       <c r="B42" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5215,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>460756</v>
+        <v>460804</v>
       </c>
       <c r="R42" t="n">
-        <v>6474585</v>
+        <v>6474592</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5245,12 +5010,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5286,19 +5051,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>114458969</v>
+        <v>114459050</v>
       </c>
       <c r="B43" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5326,10 +5086,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>460755</v>
+        <v>460648</v>
       </c>
       <c r="R43" t="n">
-        <v>6474545</v>
+        <v>6474500</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5356,17 +5116,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5402,19 +5162,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>114459075</v>
+        <v>114459052</v>
       </c>
       <c r="B44" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5442,10 +5197,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460746</v>
+        <v>460647</v>
       </c>
       <c r="R44" t="n">
-        <v>6474534</v>
+        <v>6474439</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5472,12 +5227,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5518,19 +5273,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>114458976</v>
+        <v>114459053</v>
       </c>
       <c r="B45" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5558,10 +5308,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>460840</v>
+        <v>460699</v>
       </c>
       <c r="R45" t="n">
-        <v>6474632</v>
+        <v>6474494</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5629,19 +5379,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>114459034</v>
+        <v>114459054</v>
       </c>
       <c r="B46" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5669,10 +5414,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460812</v>
+        <v>460755</v>
       </c>
       <c r="R46" t="n">
-        <v>6474536</v>
+        <v>6474474</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5699,12 +5444,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5740,19 +5485,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>114458971</v>
+        <v>114459055</v>
       </c>
       <c r="B47" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5780,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>460817</v>
+        <v>460764</v>
       </c>
       <c r="R47" t="n">
-        <v>6474535</v>
+        <v>6474490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5810,17 +5550,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5856,19 +5591,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>114459053</v>
+        <v>114459056</v>
       </c>
       <c r="B48" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5896,10 +5626,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>460699</v>
+        <v>460800</v>
       </c>
       <c r="R48" t="n">
-        <v>6474494</v>
+        <v>6474582</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5926,12 +5656,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,19 +5702,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>114459023</v>
+        <v>114459057</v>
       </c>
       <c r="B49" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -6007,10 +5737,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>460706</v>
+        <v>460786</v>
       </c>
       <c r="R49" t="n">
-        <v>6474574</v>
+        <v>6474581</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6043,6 +5773,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6078,19 +5813,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>114459067</v>
+        <v>114459058</v>
       </c>
       <c r="B50" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -6118,10 +5848,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>460719</v>
+        <v>460746</v>
       </c>
       <c r="R50" t="n">
-        <v>6474528</v>
+        <v>6474596</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6154,6 +5884,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6189,19 +5924,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>114459057</v>
+        <v>114459059</v>
       </c>
       <c r="B51" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6229,10 +5959,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>460786</v>
+        <v>460730</v>
       </c>
       <c r="R51" t="n">
-        <v>6474581</v>
+        <v>6474604</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6265,11 +5995,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6308,16 +6033,11 @@
         <v>114459065</v>
       </c>
       <c r="B52" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6416,19 +6136,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>114459071</v>
+        <v>114459066</v>
       </c>
       <c r="B53" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6456,10 +6171,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>460670</v>
+        <v>460696</v>
       </c>
       <c r="R53" t="n">
-        <v>6474470</v>
+        <v>6474532</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6492,6 +6207,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,19 +6247,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>114459074</v>
+        <v>114459067</v>
       </c>
       <c r="B54" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6567,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>460771</v>
+        <v>460719</v>
       </c>
       <c r="R54" t="n">
-        <v>6474536</v>
+        <v>6474528</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6638,19 +6353,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>114459043</v>
+        <v>114459068</v>
       </c>
       <c r="B55" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6678,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>460804</v>
+        <v>460680</v>
       </c>
       <c r="R55" t="n">
-        <v>6474592</v>
+        <v>6474546</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6708,12 +6418,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6749,19 +6459,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>114458974</v>
+        <v>114459069</v>
       </c>
       <c r="B56" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6789,10 +6494,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>460820</v>
+        <v>460620</v>
       </c>
       <c r="R56" t="n">
-        <v>6474529</v>
+        <v>6474472</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6829,7 +6534,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6865,15 +6570,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>114459250</v>
+        <v>114459070</v>
       </c>
       <c r="B57" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6881,21 +6581,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6905,10 +6605,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>460756</v>
+        <v>460673</v>
       </c>
       <c r="R57" t="n">
-        <v>6474585</v>
+        <v>6474452</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6941,6 +6641,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6976,19 +6681,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>114459005</v>
+        <v>114459071</v>
       </c>
       <c r="B58" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -7016,10 +6716,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>460715</v>
+        <v>460670</v>
       </c>
       <c r="R58" t="n">
-        <v>6474585</v>
+        <v>6474470</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7046,12 +6746,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7087,19 +6787,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>114459024</v>
+        <v>114459072</v>
       </c>
       <c r="B59" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -7127,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>460724</v>
+        <v>460703</v>
       </c>
       <c r="R59" t="n">
-        <v>6474568</v>
+        <v>6474488</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7198,19 +6893,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>114459033</v>
+        <v>114459073</v>
       </c>
       <c r="B60" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -7238,10 +6928,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>460805</v>
+        <v>460779</v>
       </c>
       <c r="R60" t="n">
-        <v>6474543</v>
+        <v>6474536</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7309,19 +6999,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>114459029</v>
+        <v>114459074</v>
       </c>
       <c r="B61" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -7349,10 +7034,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>460758</v>
+        <v>460771</v>
       </c>
       <c r="R61" t="n">
-        <v>6474546</v>
+        <v>6474536</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7420,19 +7105,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>114459040</v>
+        <v>114459075</v>
       </c>
       <c r="B62" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -7460,10 +7140,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>460819</v>
+        <v>460746</v>
       </c>
       <c r="R62" t="n">
-        <v>6474548</v>
+        <v>6474534</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7490,12 +7170,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7531,19 +7216,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>114458968</v>
+        <v>114459076</v>
       </c>
       <c r="B63" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -7571,10 +7251,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>460753</v>
+        <v>460783</v>
       </c>
       <c r="R63" t="n">
-        <v>6474552</v>
+        <v>6474520</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7611,7 +7291,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7640,6 +7320,874 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>114459077</v>
+      </c>
+      <c r="B64" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skallhult-Ripanäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>460787</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6474533</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>114459078</v>
+      </c>
+      <c r="B65" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skallhult-Ripanäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>460792</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6474530</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>114459079</v>
+      </c>
+      <c r="B66" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skallhult-Ripanäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>460807</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6474521</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>114459087</v>
+      </c>
+      <c r="B67" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skallhult-Ripanäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>460760</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6474595</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>114459088</v>
+      </c>
+      <c r="B68" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skallhult-Ripanäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>460808</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6474518</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>flera svampkroppar runt äldre tall</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>114459240</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skallhult-Ripanäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>460697</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6474537</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>114459269</v>
+      </c>
+      <c r="B70" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skallhult-Ripanäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>460764</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6474490</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>flera stora ex.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>114459270</v>
+      </c>
+      <c r="B71" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skallhult-Ripanäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>460784</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6474507</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
         <is>
           <t>Sandbarrskog Västra Götaland</t>
         </is>

--- a/artfynd/A 27703-2023 artfynd.xlsx
+++ b/artfynd/A 27703-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458877</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458968</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458969</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458970</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458971</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458974</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114458976</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459003</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459005</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1974,6 +2034,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459007</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459008</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2186,6 +2256,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459010</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459013</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2398,6 +2478,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459015</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2504,6 +2589,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459016</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2610,6 +2700,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459017</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2716,6 +2811,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459018</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459019</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2928,6 +3033,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459020</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3034,6 +3144,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459021</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3140,6 +3255,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459022</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3246,6 +3366,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459023</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3352,6 +3477,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459024</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3458,6 +3588,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3564,6 +3699,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3670,6 +3810,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3776,6 +3921,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459031</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3988,6 +4143,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459032</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4094,6 +4254,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459033</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4200,6 +4365,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459034</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4306,6 +4476,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459035</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4412,6 +4587,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4518,6 +4698,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459037</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4624,6 +4809,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4730,6 +4920,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459040</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4836,6 +5031,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459041</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4942,6 +5142,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459042</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5048,6 +5253,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459043</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5159,6 +5369,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459050</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5270,6 +5485,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459052</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5376,6 +5596,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459053</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5482,6 +5707,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459054</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5588,6 +5818,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459055</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5699,6 +5934,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459056</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5810,6 +6050,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459057</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5921,6 +6166,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459058</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6027,6 +6277,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459059</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6133,6 +6388,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459065</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6244,6 +6504,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459066</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6350,6 +6615,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459067</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6456,6 +6726,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459068</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6567,6 +6842,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459069</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6678,6 +6958,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459070</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6784,6 +7069,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459071</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6890,6 +7180,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459072</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6996,6 +7291,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459073</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7102,6 +7402,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459074</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7213,6 +7518,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459075</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7324,6 +7634,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459076</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7430,6 +7745,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459077</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7541,6 +7861,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459078</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7652,6 +7977,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459079</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7758,6 +8088,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459087</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7869,6 +8204,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459088</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7975,6 +8315,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459240</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8086,6 +8431,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459269</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8192,8 +8542,85 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114459270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>